--- a/Data/FlightPlan/FPL_08SEP26.xlsx
+++ b/Data/FlightPlan/FPL_08SEP26.xlsx
@@ -350,6 +350,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:10</t>
+  </si>
+  <si>
     <t>TPE</t>
   </si>
   <si>
@@ -644,9 +647,6 @@
     <t>VN-A575</t>
   </si>
   <si>
-    <t>07:10</t>
-  </si>
-  <si>
     <t>10:05</t>
   </si>
   <si>
@@ -1166,7 +1166,7 @@
     <t>Total Record(s): 340</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 08, 2026 02:03</t>
+    <t xml:space="preserve">Generated on  Sep 08, 2026 04:00</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3234,7 +3234,9 @@
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
+      <c t="s" r="M57" s="7">
+        <v>113</v>
+      </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c t="s" r="A58" s="6">
@@ -3257,13 +3259,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I58" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3287,7 +3289,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>17</v>
@@ -3362,7 +3364,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3371,13 +3373,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I62" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3395,19 +3397,19 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>54</v>
@@ -3428,7 +3430,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3437,13 +3439,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="I64" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3461,19 +3463,19 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>58</v>
@@ -3509,7 +3511,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3521,10 +3523,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3542,7 +3544,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3554,10 +3556,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3575,7 +3577,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3584,10 +3586,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>51</v>
@@ -3608,13 +3610,13 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>25</v>
@@ -3623,7 +3625,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3641,7 +3643,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3653,10 +3655,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3674,7 +3676,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3689,7 +3691,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3707,7 +3709,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3719,10 +3721,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3740,7 +3742,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3755,7 +3757,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3788,7 +3790,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3800,7 +3802,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>112</v>
@@ -3821,7 +3823,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3833,10 +3835,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3854,7 +3856,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3863,7 +3865,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>19</v>
@@ -3887,13 +3889,13 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>33</v>
@@ -3902,7 +3904,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3920,7 +3922,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3929,10 +3931,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>103</v>
@@ -3953,13 +3955,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>33</v>
@@ -3968,7 +3970,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4001,7 +4003,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4034,7 +4036,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4049,7 +4051,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4067,7 +4069,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4082,7 +4084,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4100,7 +4102,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4112,7 +4114,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>36</v>
@@ -4133,7 +4135,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4145,10 +4147,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4166,7 +4168,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4178,10 +4180,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4214,7 +4216,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4226,10 +4228,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4247,7 +4249,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4259,10 +4261,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4280,7 +4282,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4292,10 +4294,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4313,7 +4315,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4346,7 +4348,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4358,10 +4360,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4379,7 +4381,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4391,10 +4393,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4427,7 +4429,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4436,13 +4438,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="I97" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4460,22 +4462,22 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4493,7 +4495,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4505,10 +4507,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4526,7 +4528,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4538,10 +4540,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4574,7 +4576,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4607,7 +4609,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4622,7 +4624,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4640,7 +4642,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4649,13 +4651,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="I104" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4673,22 +4675,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4721,7 +4723,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4733,10 +4735,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4754,7 +4756,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4763,13 +4765,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4787,13 +4789,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>33</v>
@@ -4802,7 +4804,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4820,7 +4822,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4832,7 +4834,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>78</v>
@@ -4868,7 +4870,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4880,17 +4882,17 @@
         <v>25</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>85</v>
       </c>
       <c t="s" r="K112" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -4905,7 +4907,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4914,7 +4916,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>35</v>
@@ -4938,22 +4940,22 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4986,7 +4988,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -4995,13 +4997,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5019,22 +5021,22 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5052,7 +5054,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5064,10 +5066,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5085,7 +5087,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5097,10 +5099,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5118,7 +5120,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5130,7 +5132,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>47</v>
@@ -5166,7 +5168,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5181,7 +5183,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5199,7 +5201,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5208,13 +5210,13 @@
         <v>88</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I123" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5232,13 +5234,13 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>48</v>
@@ -5247,7 +5249,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5265,7 +5267,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5274,13 +5276,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5298,13 +5300,13 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>88</v>
@@ -5327,11 +5329,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C127" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5343,10 +5345,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5360,11 +5362,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C128" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5373,13 +5375,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5412,7 +5414,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5424,10 +5426,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5441,11 +5443,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C131" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5460,7 +5462,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5474,11 +5476,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C132" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5487,13 +5489,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5507,17 +5509,17 @@
         <v>5069</v>
       </c>
       <c t="s" r="C133" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>33</v>
@@ -5526,7 +5528,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5552,14 +5554,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B135" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="C135" s="7">
         <v>14</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5568,16 +5570,16 @@
         <v>25</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>61</v>
       </c>
       <c t="s" r="K135" s="7">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
@@ -5596,13 +5598,13 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>25</v>
@@ -5629,7 +5631,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5638,10 +5640,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>213</v>
@@ -5662,13 +5664,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>25</v>
@@ -5677,7 +5679,7 @@
         <v>214</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5695,7 +5697,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5728,7 +5730,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5761,7 +5763,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5776,7 +5778,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5794,7 +5796,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5920,7 +5922,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>65</v>
@@ -6037,7 +6039,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6100,10 +6102,10 @@
         <v>228</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6181,7 +6183,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>109</v>
@@ -6292,10 +6294,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>235</v>
@@ -6322,7 +6324,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>45</v>
@@ -6358,10 +6360,10 @@
         <v>45</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>237</v>
@@ -6388,7 +6390,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>45</v>
@@ -6411,7 +6413,7 @@
         <v>8020</v>
       </c>
       <c t="s" r="C163" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
@@ -6427,7 +6429,7 @@
         <v>239</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>240</v>
@@ -6444,7 +6446,7 @@
         <v>8021</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
@@ -6511,7 +6513,7 @@
         <v>244</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6538,10 +6540,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>35</v>
@@ -6568,7 +6570,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>33</v>
@@ -6607,7 +6609,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>89</v>
@@ -6673,10 +6675,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6721,7 +6723,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>248</v>
@@ -6754,10 +6756,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6787,7 +6789,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>54</v>
@@ -6823,7 +6825,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6853,10 +6855,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6934,10 +6936,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6967,7 +6969,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>223</v>
@@ -7261,10 +7263,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7330,7 +7332,7 @@
         <v>260</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7360,7 +7362,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>261</v>
@@ -7438,7 +7440,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>265</v>
@@ -7468,7 +7470,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>33</v>
@@ -7507,10 +7509,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7540,7 +7542,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>215</v>
@@ -7657,7 +7659,7 @@
         <v>269</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7699,7 +7701,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I206" s="7">
         <v>271</v>
@@ -7729,13 +7731,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>258</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>273</v>
@@ -7765,7 +7767,7 @@
         <v>258</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I208" s="7">
         <v>274</v>
@@ -7795,7 +7797,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>25</v>
@@ -7849,7 +7851,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>276</v>
@@ -7882,10 +7884,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7951,7 +7953,7 @@
         <v>266</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8017,7 +8019,7 @@
         <v>277</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8059,7 +8061,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I218" s="7">
         <v>244</v>
@@ -8089,16 +8091,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>280</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8122,16 +8124,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>281</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8155,7 +8157,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>25</v>
@@ -8230,7 +8232,7 @@
         <v>274</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8260,7 +8262,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>26</v>
@@ -8338,13 +8340,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8368,7 +8370,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>25</v>
@@ -8410,7 +8412,7 @@
         <v>286</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8470,13 +8472,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>288</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8500,7 +8502,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>25</v>
@@ -8557,7 +8559,7 @@
         <v>290</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8590,7 +8592,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8650,10 +8652,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>66</v>
@@ -8680,7 +8682,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>25</v>
@@ -8689,7 +8691,7 @@
         <v>268</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8734,10 +8736,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8800,7 +8802,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>92</v>
@@ -8848,10 +8850,10 @@
         <v>294</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8932,7 +8934,7 @@
         <v>265</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -8962,10 +8964,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9031,7 +9033,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9139,7 +9141,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>303</v>
@@ -9169,7 +9171,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>25</v>
@@ -9241,7 +9243,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>304</v>
@@ -9277,7 +9279,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9307,7 +9309,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>305</v>
@@ -9472,7 +9474,7 @@
         <v>310</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9532,7 +9534,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>236</v>
@@ -9562,13 +9564,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>311</v>
@@ -9892,13 +9894,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>248</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9922,7 +9924,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>25</v>
@@ -9958,13 +9960,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -9988,7 +9990,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>25</v>
@@ -9997,7 +9999,7 @@
         <v>320</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10045,7 +10047,7 @@
         <v>253</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10111,7 +10113,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10174,7 +10176,7 @@
         <v>324</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>41</v>
@@ -10207,7 +10209,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>244</v>
@@ -10288,7 +10290,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>326</v>
@@ -10318,13 +10320,13 @@
         <v>45</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>214</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10348,13 +10350,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>268</v>
@@ -10387,7 +10389,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>282</v>
@@ -10498,7 +10500,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>83</v>
@@ -10528,7 +10530,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>48</v>
@@ -10537,7 +10539,7 @@
         <v>291</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10567,10 +10569,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10633,10 +10635,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10747,7 +10749,7 @@
         <v>322</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>223</v>
@@ -10780,7 +10782,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>24</v>
@@ -10813,7 +10815,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>40</v>
@@ -10864,7 +10866,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10891,13 +10893,13 @@
         <v>33</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10921,13 +10923,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>331</v>
@@ -11038,7 +11040,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>336</v>
@@ -11068,7 +11070,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>25</v>
@@ -11143,7 +11145,7 @@
         <v>338</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11188,10 +11190,10 @@
         <v>340</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11221,7 +11223,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>287</v>
@@ -11257,7 +11259,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11299,13 +11301,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11329,16 +11331,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11362,13 +11364,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>323</v>
@@ -11395,7 +11397,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>222</v>
@@ -11431,7 +11433,7 @@
         <v>222</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>75</v>
@@ -11461,7 +11463,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>44</v>
@@ -11470,7 +11472,7 @@
         <v>342</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11551,7 +11553,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11665,7 +11667,7 @@
         <v>347</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11698,7 +11700,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11776,7 +11778,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>347</v>
@@ -11904,7 +11906,7 @@
         <v>13</v>
       </c>
       <c r="B347" s="7">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
@@ -11923,10 +11925,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -11937,7 +11939,7 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
@@ -11956,10 +11958,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>347</v>
+        <v>81</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -11970,7 +11972,7 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>629</v>
+        <v>720</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
@@ -11986,13 +11988,13 @@
         <v>45</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>259</v>
+        <v>154</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12003,7 +12005,7 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>636</v>
+        <v>721</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
@@ -12016,16 +12018,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>45</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>109</v>
+        <v>326</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12036,7 +12038,7 @@
         <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
@@ -12052,13 +12054,13 @@
         <v>45</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c t="s" r="I351" s="7">
+        <v>115</v>
+      </c>
+      <c t="s" r="J351" s="7">
         <v>227</v>
-      </c>
-      <c t="s" r="J351" s="7">
-        <v>287</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12069,7 +12071,7 @@
         <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>312</v>
+        <v>704</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
@@ -12082,65 +12084,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>66</v>
+        <v>311</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c t="s" r="A353" s="6">
-        <v>13</v>
-      </c>
-      <c r="B353" s="7">
-        <v>311</v>
-      </c>
-      <c t="s" r="C353" s="7">
-        <v>14</v>
-      </c>
+      <c r="A353" s="6"/>
+      <c r="B353" s="7"/>
+      <c r="C353" s="7"/>
       <c r="D353" s="7"/>
-      <c t="s" r="E353" s="7">
-        <v>349</v>
-      </c>
-      <c r="F353" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G353" s="8">
-        <v>82</v>
-      </c>
-      <c t="s" r="H353" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I353" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="J353" s="7">
-        <v>105</v>
-      </c>
+      <c r="E353" s="7"/>
+      <c r="F353" s="7"/>
+      <c r="G353" s="8"/>
+      <c r="H353" s="8"/>
+      <c r="I353" s="7"/>
+      <c r="J353" s="7"/>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
     </row>
     <row r="354" ht="14.25" customHeight="1">
-      <c r="A354" s="6"/>
-      <c r="B354" s="7"/>
-      <c r="C354" s="7"/>
+      <c t="s" r="A354" s="6">
+        <v>13</v>
+      </c>
+      <c r="B354" s="7">
+        <v>959</v>
+      </c>
+      <c t="s" r="C354" s="7">
+        <v>14</v>
+      </c>
       <c r="D354" s="7"/>
-      <c r="E354" s="7"/>
-      <c r="F354" s="7"/>
-      <c r="G354" s="8"/>
-      <c r="H354" s="8"/>
-      <c r="I354" s="7"/>
-      <c r="J354" s="7"/>
+      <c t="s" r="E354" s="7">
+        <v>350</v>
+      </c>
+      <c r="F354" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G354" s="8">
+        <v>351</v>
+      </c>
+      <c t="s" r="H354" s="8">
+        <v>33</v>
+      </c>
+      <c t="s" r="I354" s="7">
+        <v>281</v>
+      </c>
+      <c t="s" r="J354" s="7">
+        <v>34</v>
+      </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c r="M354" s="7"/>
@@ -12150,7 +12152,7 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>959</v>
+        <v>143</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
@@ -12163,16 +12165,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>351</v>
+        <v>33</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>281</v>
+        <v>86</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12183,7 +12185,7 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
@@ -12196,65 +12198,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H356" s="8">
         <v>33</v>
       </c>
-      <c t="s" r="H356" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I356" s="7">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>352</v>
+        <v>308</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
     </row>
     <row r="357" ht="14.25" customHeight="1">
-      <c t="s" r="A357" s="6">
-        <v>13</v>
-      </c>
-      <c r="B357" s="7">
-        <v>146</v>
-      </c>
-      <c t="s" r="C357" s="7">
-        <v>14</v>
-      </c>
+      <c r="A357" s="6"/>
+      <c r="B357" s="7"/>
+      <c r="C357" s="7"/>
       <c r="D357" s="7"/>
-      <c t="s" r="E357" s="7">
-        <v>350</v>
-      </c>
-      <c r="F357" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G357" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H357" s="8">
-        <v>33</v>
-      </c>
-      <c t="s" r="I357" s="7">
-        <v>37</v>
-      </c>
-      <c t="s" r="J357" s="7">
-        <v>308</v>
-      </c>
+      <c r="E357" s="7"/>
+      <c r="F357" s="7"/>
+      <c r="G357" s="8"/>
+      <c r="H357" s="8"/>
+      <c r="I357" s="7"/>
+      <c r="J357" s="7"/>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c r="M357" s="7"/>
     </row>
     <row r="358" ht="14.25" customHeight="1">
-      <c r="A358" s="6"/>
-      <c r="B358" s="7"/>
-      <c r="C358" s="7"/>
+      <c t="s" r="A358" s="6">
+        <v>13</v>
+      </c>
+      <c r="B358" s="7">
+        <v>625</v>
+      </c>
+      <c t="s" r="C358" s="7">
+        <v>14</v>
+      </c>
       <c r="D358" s="7"/>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
-      <c r="G358" s="8"/>
-      <c r="H358" s="8"/>
-      <c r="I358" s="7"/>
-      <c r="J358" s="7"/>
+      <c t="s" r="E358" s="7">
+        <v>353</v>
+      </c>
+      <c r="F358" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G358" s="8">
+        <v>45</v>
+      </c>
+      <c t="s" r="H358" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I358" s="7">
+        <v>113</v>
+      </c>
+      <c t="s" r="J358" s="7">
+        <v>31</v>
+      </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
@@ -12264,7 +12266,7 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
@@ -12277,16 +12279,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H359" s="8">
         <v>45</v>
       </c>
-      <c t="s" r="H359" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I359" s="7">
-        <v>58</v>
+        <v>271</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>46</v>
+        <v>347</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12297,7 +12299,7 @@
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
@@ -12310,16 +12312,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12330,7 +12332,7 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>720</v>
+        <v>636</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
@@ -12343,16 +12345,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H361" s="8">
         <v>45</v>
       </c>
-      <c t="s" r="H361" s="8">
-        <v>184</v>
-      </c>
       <c t="s" r="I361" s="7">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12363,7 +12365,7 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>721</v>
+        <v>633</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
@@ -12376,16 +12378,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>326</v>
+        <v>227</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>189</v>
+        <v>287</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12396,7 +12398,7 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>703</v>
+        <v>312</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
@@ -12409,16 +12411,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12429,7 +12431,7 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>704</v>
+        <v>311</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
@@ -12442,16 +12444,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12529,10 +12531,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12595,10 +12597,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12742,7 +12744,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>211</v>
+        <v>113</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>31</v>
@@ -12778,7 +12780,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12811,7 +12813,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12844,7 +12846,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12904,7 +12906,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>357</v>
@@ -12934,13 +12936,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>359</v>
@@ -13090,7 +13092,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13165,7 +13167,7 @@
         <v>33</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>362</v>
@@ -13195,7 +13197,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>33</v>
@@ -13204,7 +13206,7 @@
         <v>268</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13279,7 +13281,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>271</v>
@@ -13309,13 +13311,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>367</v>
@@ -13345,13 +13347,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13375,7 +13377,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>25</v>
@@ -13495,7 +13497,7 @@
         <v>373</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>27</v>
@@ -13528,10 +13530,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13579,7 +13581,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13660,7 +13662,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13690,7 +13692,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>304</v>
@@ -13738,7 +13740,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>265</v>
@@ -13829,7 +13831,7 @@
       </c>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -13907,7 +13909,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13937,10 +13939,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -13985,10 +13987,10 @@
         <v>107</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14018,10 +14020,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
